--- a/task3_garbage_duplicates_clean.xlsx
+++ b/task3_garbage_duplicates_clean.xlsx
@@ -482,7 +482,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>first_visit</t>
+          <t>первичный визит</t>
         </is>
       </c>
     </row>
@@ -515,7 +515,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>first_visit</t>
+          <t>первичный визит</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>repeat_visit</t>
+          <t>повторный визит</t>
         </is>
       </c>
     </row>
@@ -581,7 +581,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>first_visit</t>
+          <t>первичный визит</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>repeat_visit</t>
+          <t>повторный визит</t>
         </is>
       </c>
     </row>
@@ -647,7 +647,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>first_visit</t>
+          <t>первичный визит</t>
         </is>
       </c>
     </row>
@@ -680,7 +680,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>repeat_visit</t>
+          <t>повторный визит</t>
         </is>
       </c>
     </row>
@@ -713,7 +713,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>first_visit</t>
+          <t>первичный визит</t>
         </is>
       </c>
     </row>
